--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.73474</v>
+        <v>16.82035</v>
       </c>
       <c r="D2" t="n">
-        <v>16.61599</v>
+        <v>16.12983</v>
       </c>
       <c r="E2" t="n">
-        <v>16.57406</v>
+        <v>16.78907</v>
       </c>
       <c r="F2" t="n">
-        <v>42.07377</v>
+        <v>43.46648</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05112</v>
+        <v>0.0505</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80381</v>
+        <v>1.80075</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.70003</v>
+        <v>16.83108</v>
       </c>
       <c r="D3" t="n">
-        <v>16.43602</v>
+        <v>16.45102</v>
       </c>
       <c r="E3" t="n">
-        <v>16.56779</v>
+        <v>16.75312</v>
       </c>
       <c r="F3" t="n">
-        <v>42.14995</v>
+        <v>42.24422</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05072</v>
+        <v>0.05029</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81494</v>
+        <v>1.82484</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.64323</v>
+        <v>16.59734</v>
       </c>
       <c r="D4" t="n">
-        <v>16.01548</v>
+        <v>16.34835</v>
       </c>
       <c r="E4" t="n">
-        <v>16.7682</v>
+        <v>16.38704</v>
       </c>
       <c r="F4" t="n">
-        <v>42.24177</v>
+        <v>42.30393</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04833</v>
+        <v>0.05184</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81244</v>
+        <v>1.80712</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.55493</v>
+        <v>16.52524</v>
       </c>
       <c r="D6" t="n">
-        <v>15.9626</v>
+        <v>15.93886</v>
       </c>
       <c r="E6" t="n">
-        <v>16.40429</v>
+        <v>16.31745</v>
       </c>
       <c r="F6" t="n">
-        <v>21.26843</v>
+        <v>21.60607</v>
       </c>
       <c r="G6" t="n">
-        <v>33.92232</v>
+        <v>34.52735</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.77474</v>
+        <v>16.48298</v>
       </c>
       <c r="D7" t="n">
-        <v>15.86057</v>
+        <v>16.18141</v>
       </c>
       <c r="E7" t="n">
-        <v>16.13448</v>
+        <v>16.35806</v>
       </c>
       <c r="F7" t="n">
-        <v>21.6083</v>
+        <v>21.8223</v>
       </c>
       <c r="G7" t="n">
-        <v>34.59595</v>
+        <v>33.81619</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.74371</v>
+        <v>16.57952</v>
       </c>
       <c r="D8" t="n">
-        <v>15.8885</v>
+        <v>15.75754</v>
       </c>
       <c r="E8" t="n">
-        <v>16.07221</v>
+        <v>15.93907</v>
       </c>
       <c r="F8" t="n">
-        <v>21.71775</v>
+        <v>21.85598</v>
       </c>
       <c r="G8" t="n">
-        <v>33.16925</v>
+        <v>33.78837</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61036</v>
+        <v>0.5955</v>
       </c>
       <c r="D10" t="n">
-        <v>1.11524</v>
+        <v>1.12615</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60004</v>
+        <v>0.61137</v>
       </c>
       <c r="D11" t="n">
-        <v>1.09943</v>
+        <v>1.11571</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59727</v>
+        <v>0.61273</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10559</v>
+        <v>1.11589</v>
       </c>
     </row>
   </sheetData>
